--- a/ITI/MHD/StructureDefinition-IHE.MHD.UniqueIdIdentifier.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.UniqueIdIdentifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,9 +364,6 @@
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
-    <t>usual</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -399,6 +396,14 @@
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://profiles.ihe.net/ITI/MHD/CodeSystem/IHE.MHD.MHDIdentifierType"/&gt;
+    &lt;code value="uniqueId"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>extensible</t>
@@ -1334,7 +1339,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>89</v>
@@ -1371,28 +1376,28 @@
         <v>78</v>
       </c>
       <c r="S5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X5" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="T5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X5" t="s" s="2">
+      <c r="Y5" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="Z5" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>78</v>
@@ -1425,10 +1430,10 @@
         <v>85</v>
       </c>
       <c r="AK5" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>78</v>
@@ -1436,10 +1441,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1447,7 +1452,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>89</v>
@@ -1462,19 +1467,19 @@
         <v>107</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="N6" t="s" s="2">
+      <c r="O6" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>78</v>
@@ -1484,7 +1489,7 @@
         <v>78</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="T6" t="s" s="2">
         <v>78</v>
@@ -1523,7 +1528,7 @@
         <v>78</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
@@ -1541,7 +1546,7 @@
         <v>128</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>78</v>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.UniqueIdIdentifier.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.UniqueIdIdentifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
